--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -2581,7 +2581,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.590551181102362" bottom="0.590551181102362" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
+  <pageSetup paperSize="9" scale="96" orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -4933,9 +4933,9 @@
     <mergeCell ref="AA2:AB3"/>
     <mergeCell ref="AC2:AD3"/>
   </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="1" gridLines="1"/>
   <pageMargins left="0" right="0" top="0.275590551181102" bottom="0.275590551181102" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
+  <pageSetup paperSize="9" scale="91" orientation="landscape"/>
   <headerFooter/>
 </worksheet>
 </file>